--- a/artfynd/A 14156-2026 artfynd.xlsx
+++ b/artfynd/A 14156-2026 artfynd.xlsx
@@ -1206,10 +1206,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132089853</v>
+        <v>132089866</v>
       </c>
       <c r="B7" t="n">
-        <v>5199</v>
+        <v>96417</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1217,39 +1217,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>105930</v>
+        <v>2667</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Trestickan, Boh</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>316907</v>
+        <v>316660</v>
       </c>
       <c r="R7" t="n">
-        <v>6513455</v>
+        <v>6513174</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1292,21 +1287,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1323,10 +1303,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132089850</v>
+        <v>132089853</v>
       </c>
       <c r="B8" t="n">
-        <v>8444</v>
+        <v>5199</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1334,21 +1314,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106554</v>
+        <v>105930</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1363,10 +1343,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>316736</v>
+        <v>316907</v>
       </c>
       <c r="R8" t="n">
-        <v>6513476</v>
+        <v>6513455</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1409,6 +1389,21 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1425,10 +1420,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132089866</v>
+        <v>132089850</v>
       </c>
       <c r="B9" t="n">
-        <v>96414</v>
+        <v>8444</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1436,34 +1431,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2667</v>
+        <v>106554</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Trestickan, Boh</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>316660</v>
+        <v>316736</v>
       </c>
       <c r="R9" t="n">
-        <v>6513174</v>
+        <v>6513476</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1522,10 +1522,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132089843</v>
+        <v>132089863</v>
       </c>
       <c r="B10" t="n">
-        <v>91873</v>
+        <v>96419</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1533,21 +1533,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4660</v>
+        <v>2666</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Grov fjädermossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Exsertotheca crispa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1557,10 +1557,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>316707</v>
+        <v>316673</v>
       </c>
       <c r="R10" t="n">
-        <v>6513460</v>
+        <v>6513287</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1603,21 +1603,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1634,10 +1619,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132089863</v>
+        <v>132089843</v>
       </c>
       <c r="B11" t="n">
-        <v>96416</v>
+        <v>91876</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1645,21 +1630,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2666</v>
+        <v>4660</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grov fjädermossa</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Exsertotheca crispa</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1669,10 +1654,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>316673</v>
+        <v>316707</v>
       </c>
       <c r="R11" t="n">
-        <v>6513287</v>
+        <v>6513460</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1715,6 +1700,21 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1734,7 +1734,7 @@
         <v>132089842</v>
       </c>
       <c r="B12" t="n">
-        <v>91873</v>
+        <v>91876</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2200,7 +2200,7 @@
         <v>132089840</v>
       </c>
       <c r="B16" t="n">
-        <v>91852</v>
+        <v>91855</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2312,7 +2312,7 @@
         <v>132089851</v>
       </c>
       <c r="B17" t="n">
-        <v>96416</v>
+        <v>96419</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
         <v>132089848</v>
       </c>
       <c r="B18" t="n">
-        <v>96414</v>
+        <v>96417</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2521,7 +2521,7 @@
         <v>132089841</v>
       </c>
       <c r="B19" t="n">
-        <v>96416</v>
+        <v>96419</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
         <v>132089845</v>
       </c>
       <c r="B20" t="n">
-        <v>91946</v>
+        <v>91949</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         <v>132089865</v>
       </c>
       <c r="B21" t="n">
-        <v>96416</v>
+        <v>96419</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2813,7 +2813,7 @@
         <v>132089862</v>
       </c>
       <c r="B22" t="n">
-        <v>92696</v>
+        <v>92699</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         <v>132089861</v>
       </c>
       <c r="B23" t="n">
-        <v>91946</v>
+        <v>91949</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3038,7 +3038,7 @@
         <v>132089847</v>
       </c>
       <c r="B24" t="n">
-        <v>96416</v>
+        <v>96419</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 14156-2026 artfynd.xlsx
+++ b/artfynd/A 14156-2026 artfynd.xlsx
@@ -2615,10 +2615,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132089845</v>
+        <v>132089865</v>
       </c>
       <c r="B20" t="n">
-        <v>91949</v>
+        <v>96419</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2626,21 +2626,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5321</v>
+        <v>2666</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Grov fjädermossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Exsertotheca crispa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2650,10 +2650,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>316211</v>
+        <v>316663</v>
       </c>
       <c r="R20" t="n">
-        <v>6513458</v>
+        <v>6513178</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2694,7 +2694,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2713,10 +2712,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132089865</v>
+        <v>132089845</v>
       </c>
       <c r="B21" t="n">
-        <v>96419</v>
+        <v>91949</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2724,21 +2723,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2666</v>
+        <v>5321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Grov fjädermossa</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Exsertotheca crispa</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2748,10 +2747,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>316663</v>
+        <v>316211</v>
       </c>
       <c r="R21" t="n">
-        <v>6513178</v>
+        <v>6513458</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2792,6 +2791,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 14156-2026 artfynd.xlsx
+++ b/artfynd/A 14156-2026 artfynd.xlsx
@@ -1206,10 +1206,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132089866</v>
+        <v>132089853</v>
       </c>
       <c r="B7" t="n">
-        <v>96417</v>
+        <v>5199</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1217,34 +1217,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2667</v>
+        <v>105930</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Trestickan, Boh</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>316660</v>
+        <v>316907</v>
       </c>
       <c r="R7" t="n">
-        <v>6513174</v>
+        <v>6513455</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1287,6 +1292,21 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1303,10 +1323,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132089853</v>
+        <v>132089850</v>
       </c>
       <c r="B8" t="n">
-        <v>5199</v>
+        <v>8444</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1314,21 +1334,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>105930</v>
+        <v>106554</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1343,10 +1363,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>316907</v>
+        <v>316736</v>
       </c>
       <c r="R8" t="n">
-        <v>6513455</v>
+        <v>6513476</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1389,21 +1409,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1420,10 +1425,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132089850</v>
+        <v>132089866</v>
       </c>
       <c r="B9" t="n">
-        <v>8444</v>
+        <v>96417</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1431,39 +1436,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106554</v>
+        <v>2667</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Trestickan, Boh</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>316736</v>
+        <v>316660</v>
       </c>
       <c r="R9" t="n">
-        <v>6513476</v>
+        <v>6513174</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -2615,10 +2615,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132089865</v>
+        <v>132089845</v>
       </c>
       <c r="B20" t="n">
-        <v>96419</v>
+        <v>91949</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2626,21 +2626,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2666</v>
+        <v>5321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Grov fjädermossa</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Exsertotheca crispa</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2650,10 +2650,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>316663</v>
+        <v>316211</v>
       </c>
       <c r="R20" t="n">
-        <v>6513178</v>
+        <v>6513458</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2694,6 +2694,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2712,10 +2713,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132089845</v>
+        <v>132089865</v>
       </c>
       <c r="B21" t="n">
-        <v>91949</v>
+        <v>96419</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2723,21 +2724,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5321</v>
+        <v>2666</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Grov fjädermossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Exsertotheca crispa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2747,10 +2748,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>316211</v>
+        <v>316663</v>
       </c>
       <c r="R21" t="n">
-        <v>6513458</v>
+        <v>6513178</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2791,7 +2792,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 14156-2026 artfynd.xlsx
+++ b/artfynd/A 14156-2026 artfynd.xlsx
@@ -1522,10 +1522,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132089863</v>
+        <v>132089843</v>
       </c>
       <c r="B10" t="n">
-        <v>96419</v>
+        <v>91876</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1533,21 +1533,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2666</v>
+        <v>4660</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grov fjädermossa</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Exsertotheca crispa</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1557,10 +1557,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>316673</v>
+        <v>316707</v>
       </c>
       <c r="R10" t="n">
-        <v>6513287</v>
+        <v>6513460</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1603,6 +1603,21 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1619,10 +1634,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132089843</v>
+        <v>132089863</v>
       </c>
       <c r="B11" t="n">
-        <v>91876</v>
+        <v>96419</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1630,21 +1645,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4660</v>
+        <v>2666</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Grov fjädermossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Exsertotheca crispa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1654,10 +1669,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>316707</v>
+        <v>316673</v>
       </c>
       <c r="R11" t="n">
-        <v>6513460</v>
+        <v>6513287</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1700,21 +1715,6 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -2615,10 +2615,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132089845</v>
+        <v>132089865</v>
       </c>
       <c r="B20" t="n">
-        <v>91949</v>
+        <v>96419</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2626,21 +2626,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5321</v>
+        <v>2666</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Grov fjädermossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Exsertotheca crispa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2650,10 +2650,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>316211</v>
+        <v>316663</v>
       </c>
       <c r="R20" t="n">
-        <v>6513458</v>
+        <v>6513178</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2694,7 +2694,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2713,10 +2712,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132089865</v>
+        <v>132089845</v>
       </c>
       <c r="B21" t="n">
-        <v>96419</v>
+        <v>91949</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2724,21 +2723,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2666</v>
+        <v>5321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Grov fjädermossa</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Exsertotheca crispa</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2748,10 +2747,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>316663</v>
+        <v>316211</v>
       </c>
       <c r="R21" t="n">
-        <v>6513178</v>
+        <v>6513458</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2792,6 +2791,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 14156-2026 artfynd.xlsx
+++ b/artfynd/A 14156-2026 artfynd.xlsx
@@ -1522,10 +1522,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132089843</v>
+        <v>132089863</v>
       </c>
       <c r="B10" t="n">
-        <v>91876</v>
+        <v>96419</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1533,21 +1533,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4660</v>
+        <v>2666</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Grov fjädermossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Exsertotheca crispa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1557,10 +1557,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>316707</v>
+        <v>316673</v>
       </c>
       <c r="R10" t="n">
-        <v>6513460</v>
+        <v>6513287</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1603,21 +1603,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1634,10 +1619,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132089863</v>
+        <v>132089843</v>
       </c>
       <c r="B11" t="n">
-        <v>96419</v>
+        <v>91876</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1645,21 +1630,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2666</v>
+        <v>4660</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grov fjädermossa</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Exsertotheca crispa</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1669,10 +1654,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>316673</v>
+        <v>316707</v>
       </c>
       <c r="R11" t="n">
-        <v>6513287</v>
+        <v>6513460</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1715,6 +1700,21 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">

--- a/artfynd/A 14156-2026 artfynd.xlsx
+++ b/artfynd/A 14156-2026 artfynd.xlsx
@@ -1206,10 +1206,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132089853</v>
+        <v>132089866</v>
       </c>
       <c r="B7" t="n">
-        <v>5199</v>
+        <v>96425</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1217,39 +1217,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>105930</v>
+        <v>2667</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Trestickan, Boh</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>316907</v>
+        <v>316660</v>
       </c>
       <c r="R7" t="n">
-        <v>6513455</v>
+        <v>6513174</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1292,21 +1287,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1323,10 +1303,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132089850</v>
+        <v>132089853</v>
       </c>
       <c r="B8" t="n">
-        <v>8444</v>
+        <v>5199</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1334,21 +1314,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106554</v>
+        <v>105930</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1363,10 +1343,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>316736</v>
+        <v>316907</v>
       </c>
       <c r="R8" t="n">
-        <v>6513476</v>
+        <v>6513455</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1409,6 +1389,21 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1425,10 +1420,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132089866</v>
+        <v>132089850</v>
       </c>
       <c r="B9" t="n">
-        <v>96417</v>
+        <v>8444</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1436,34 +1431,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2667</v>
+        <v>106554</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Trestickan, Boh</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>316660</v>
+        <v>316736</v>
       </c>
       <c r="R9" t="n">
-        <v>6513174</v>
+        <v>6513476</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1525,7 +1525,7 @@
         <v>132089863</v>
       </c>
       <c r="B10" t="n">
-        <v>96419</v>
+        <v>96427</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1622,7 +1622,7 @@
         <v>132089843</v>
       </c>
       <c r="B11" t="n">
-        <v>91876</v>
+        <v>91882</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1734,7 +1734,7 @@
         <v>132089842</v>
       </c>
       <c r="B12" t="n">
-        <v>91876</v>
+        <v>91882</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2080,7 +2080,7 @@
         <v>132089855</v>
       </c>
       <c r="B15" t="n">
-        <v>57945</v>
+        <v>57946</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2200,7 +2200,7 @@
         <v>132089840</v>
       </c>
       <c r="B16" t="n">
-        <v>91855</v>
+        <v>91861</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2312,7 +2312,7 @@
         <v>132089851</v>
       </c>
       <c r="B17" t="n">
-        <v>96419</v>
+        <v>96427</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
         <v>132089848</v>
       </c>
       <c r="B18" t="n">
-        <v>96417</v>
+        <v>96425</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2521,7 +2521,7 @@
         <v>132089841</v>
       </c>
       <c r="B19" t="n">
-        <v>96419</v>
+        <v>96427</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2615,10 +2615,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132089865</v>
+        <v>132089845</v>
       </c>
       <c r="B20" t="n">
-        <v>96419</v>
+        <v>91955</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2626,21 +2626,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2666</v>
+        <v>5321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Grov fjädermossa</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Exsertotheca crispa</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2650,10 +2650,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>316663</v>
+        <v>316211</v>
       </c>
       <c r="R20" t="n">
-        <v>6513178</v>
+        <v>6513458</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2694,6 +2694,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2712,10 +2713,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132089845</v>
+        <v>132089865</v>
       </c>
       <c r="B21" t="n">
-        <v>91949</v>
+        <v>96427</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2723,21 +2724,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5321</v>
+        <v>2666</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Grov fjädermossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Exsertotheca crispa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2747,10 +2748,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>316211</v>
+        <v>316663</v>
       </c>
       <c r="R21" t="n">
-        <v>6513458</v>
+        <v>6513178</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2791,7 +2792,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2813,7 +2813,7 @@
         <v>132089862</v>
       </c>
       <c r="B22" t="n">
-        <v>92699</v>
+        <v>92705</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         <v>132089861</v>
       </c>
       <c r="B23" t="n">
-        <v>91949</v>
+        <v>91955</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3038,7 +3038,7 @@
         <v>132089847</v>
       </c>
       <c r="B24" t="n">
-        <v>96419</v>
+        <v>96427</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 14156-2026 artfynd.xlsx
+++ b/artfynd/A 14156-2026 artfynd.xlsx
@@ -1209,7 +1209,7 @@
         <v>132089866</v>
       </c>
       <c r="B7" t="n">
-        <v>96425</v>
+        <v>96435</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1522,10 +1522,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132089863</v>
+        <v>132089843</v>
       </c>
       <c r="B10" t="n">
-        <v>96427</v>
+        <v>91892</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1533,21 +1533,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2666</v>
+        <v>4660</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grov fjädermossa</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Exsertotheca crispa</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1557,10 +1557,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>316673</v>
+        <v>316707</v>
       </c>
       <c r="R10" t="n">
-        <v>6513287</v>
+        <v>6513460</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1603,6 +1603,21 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1619,10 +1634,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132089843</v>
+        <v>132089863</v>
       </c>
       <c r="B11" t="n">
-        <v>91882</v>
+        <v>96437</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1630,21 +1645,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4660</v>
+        <v>2666</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Grov fjädermossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Exsertotheca crispa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1654,10 +1669,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>316707</v>
+        <v>316673</v>
       </c>
       <c r="R11" t="n">
-        <v>6513460</v>
+        <v>6513287</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1700,21 +1715,6 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1734,7 +1734,7 @@
         <v>132089842</v>
       </c>
       <c r="B12" t="n">
-        <v>91882</v>
+        <v>91892</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2080,7 +2080,7 @@
         <v>132089855</v>
       </c>
       <c r="B15" t="n">
-        <v>57946</v>
+        <v>57950</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2200,7 +2200,7 @@
         <v>132089840</v>
       </c>
       <c r="B16" t="n">
-        <v>91861</v>
+        <v>91871</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2312,7 +2312,7 @@
         <v>132089851</v>
       </c>
       <c r="B17" t="n">
-        <v>96427</v>
+        <v>96437</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
         <v>132089848</v>
       </c>
       <c r="B18" t="n">
-        <v>96425</v>
+        <v>96435</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2521,7 +2521,7 @@
         <v>132089841</v>
       </c>
       <c r="B19" t="n">
-        <v>96427</v>
+        <v>96437</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
         <v>132089845</v>
       </c>
       <c r="B20" t="n">
-        <v>91955</v>
+        <v>91965</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         <v>132089865</v>
       </c>
       <c r="B21" t="n">
-        <v>96427</v>
+        <v>96437</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2813,7 +2813,7 @@
         <v>132089862</v>
       </c>
       <c r="B22" t="n">
-        <v>92705</v>
+        <v>92715</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         <v>132089861</v>
       </c>
       <c r="B23" t="n">
-        <v>91955</v>
+        <v>91965</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3038,7 +3038,7 @@
         <v>132089847</v>
       </c>
       <c r="B24" t="n">
-        <v>96427</v>
+        <v>96437</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 14156-2026 artfynd.xlsx
+++ b/artfynd/A 14156-2026 artfynd.xlsx
@@ -1209,7 +1209,7 @@
         <v>132089866</v>
       </c>
       <c r="B7" t="n">
-        <v>96435</v>
+        <v>96437</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1525,7 +1525,7 @@
         <v>132089843</v>
       </c>
       <c r="B10" t="n">
-        <v>91892</v>
+        <v>91893</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>132089863</v>
       </c>
       <c r="B11" t="n">
-        <v>96437</v>
+        <v>96439</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1734,7 +1734,7 @@
         <v>132089842</v>
       </c>
       <c r="B12" t="n">
-        <v>91892</v>
+        <v>91893</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2200,7 +2200,7 @@
         <v>132089840</v>
       </c>
       <c r="B16" t="n">
-        <v>91871</v>
+        <v>91872</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2312,7 +2312,7 @@
         <v>132089851</v>
       </c>
       <c r="B17" t="n">
-        <v>96437</v>
+        <v>96439</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
         <v>132089848</v>
       </c>
       <c r="B18" t="n">
-        <v>96435</v>
+        <v>96437</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2521,7 +2521,7 @@
         <v>132089841</v>
       </c>
       <c r="B19" t="n">
-        <v>96437</v>
+        <v>96439</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2615,10 +2615,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132089845</v>
+        <v>132089865</v>
       </c>
       <c r="B20" t="n">
-        <v>91965</v>
+        <v>96439</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2626,21 +2626,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5321</v>
+        <v>2666</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Grov fjädermossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Exsertotheca crispa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2650,10 +2650,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>316211</v>
+        <v>316663</v>
       </c>
       <c r="R20" t="n">
-        <v>6513458</v>
+        <v>6513178</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2694,7 +2694,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2713,10 +2712,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132089865</v>
+        <v>132089845</v>
       </c>
       <c r="B21" t="n">
-        <v>96437</v>
+        <v>91966</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2724,21 +2723,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2666</v>
+        <v>5321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Grov fjädermossa</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Exsertotheca crispa</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2748,10 +2747,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>316663</v>
+        <v>316211</v>
       </c>
       <c r="R21" t="n">
-        <v>6513178</v>
+        <v>6513458</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2792,6 +2791,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2810,32 +2810,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132089862</v>
+        <v>132089861</v>
       </c>
       <c r="B22" t="n">
-        <v>92715</v>
+        <v>91966</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>717</v>
+        <v>5321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Borsttagging</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Gloiodon strigosus</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schwein. : Fr.) P. Karst.</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2845,10 +2845,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>316676</v>
+        <v>316813</v>
       </c>
       <c r="R22" t="n">
-        <v>6513293</v>
+        <v>6513496</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2889,6 +2889,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2922,32 +2923,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132089861</v>
+        <v>132089862</v>
       </c>
       <c r="B23" t="n">
-        <v>91965</v>
+        <v>92716</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5321</v>
+        <v>717</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Borsttagging</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Gloiodon strigosus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Schwein. : Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2957,10 +2958,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>316813</v>
+        <v>316676</v>
       </c>
       <c r="R23" t="n">
-        <v>6513496</v>
+        <v>6513293</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3001,7 +3002,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3038,7 +3038,7 @@
         <v>132089847</v>
       </c>
       <c r="B24" t="n">
-        <v>96437</v>
+        <v>96439</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 14156-2026 artfynd.xlsx
+++ b/artfynd/A 14156-2026 artfynd.xlsx
@@ -2615,10 +2615,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132089865</v>
+        <v>132089845</v>
       </c>
       <c r="B20" t="n">
-        <v>96439</v>
+        <v>91966</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2626,21 +2626,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2666</v>
+        <v>5321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Grov fjädermossa</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Exsertotheca crispa</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2650,10 +2650,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>316663</v>
+        <v>316211</v>
       </c>
       <c r="R20" t="n">
-        <v>6513178</v>
+        <v>6513458</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2694,6 +2694,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2712,10 +2713,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132089845</v>
+        <v>132089865</v>
       </c>
       <c r="B21" t="n">
-        <v>91966</v>
+        <v>96439</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2723,21 +2724,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5321</v>
+        <v>2666</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Grov fjädermossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Exsertotheca crispa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2747,10 +2748,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>316211</v>
+        <v>316663</v>
       </c>
       <c r="R21" t="n">
-        <v>6513458</v>
+        <v>6513178</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2791,7 +2792,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 14156-2026 artfynd.xlsx
+++ b/artfynd/A 14156-2026 artfynd.xlsx
@@ -1522,10 +1522,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132089843</v>
+        <v>132089863</v>
       </c>
       <c r="B10" t="n">
-        <v>91893</v>
+        <v>96439</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1533,21 +1533,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4660</v>
+        <v>2666</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Grov fjädermossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Exsertotheca crispa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1557,10 +1557,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>316707</v>
+        <v>316673</v>
       </c>
       <c r="R10" t="n">
-        <v>6513460</v>
+        <v>6513287</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1603,21 +1603,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1634,10 +1619,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132089863</v>
+        <v>132089843</v>
       </c>
       <c r="B11" t="n">
-        <v>96439</v>
+        <v>91893</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1645,21 +1630,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2666</v>
+        <v>4660</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grov fjädermossa</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Exsertotheca crispa</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1669,10 +1654,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>316673</v>
+        <v>316707</v>
       </c>
       <c r="R11" t="n">
-        <v>6513287</v>
+        <v>6513460</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1715,6 +1700,21 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -2615,10 +2615,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132089845</v>
+        <v>132089865</v>
       </c>
       <c r="B20" t="n">
-        <v>91966</v>
+        <v>96439</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2626,21 +2626,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5321</v>
+        <v>2666</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Grov fjädermossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Exsertotheca crispa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2650,10 +2650,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>316211</v>
+        <v>316663</v>
       </c>
       <c r="R20" t="n">
-        <v>6513458</v>
+        <v>6513178</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2694,7 +2694,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2713,10 +2712,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132089865</v>
+        <v>132089845</v>
       </c>
       <c r="B21" t="n">
-        <v>96439</v>
+        <v>91966</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2724,21 +2723,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2666</v>
+        <v>5321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Grov fjädermossa</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Exsertotheca crispa</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2748,10 +2747,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>316663</v>
+        <v>316211</v>
       </c>
       <c r="R21" t="n">
-        <v>6513178</v>
+        <v>6513458</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2792,6 +2791,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2810,32 +2810,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132089861</v>
+        <v>132089862</v>
       </c>
       <c r="B22" t="n">
-        <v>91966</v>
+        <v>92716</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5321</v>
+        <v>717</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Borsttagging</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Gloiodon strigosus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Schwein. : Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2845,10 +2845,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>316813</v>
+        <v>316676</v>
       </c>
       <c r="R22" t="n">
-        <v>6513496</v>
+        <v>6513293</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2889,7 +2889,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2923,32 +2922,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132089862</v>
+        <v>132089861</v>
       </c>
       <c r="B23" t="n">
-        <v>92716</v>
+        <v>91966</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>717</v>
+        <v>5321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Borsttagging</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Gloiodon strigosus</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schwein. : Fr.) P. Karst.</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2958,10 +2957,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>316676</v>
+        <v>316813</v>
       </c>
       <c r="R23" t="n">
-        <v>6513293</v>
+        <v>6513496</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3002,6 +3001,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 14156-2026 artfynd.xlsx
+++ b/artfynd/A 14156-2026 artfynd.xlsx
@@ -1206,10 +1206,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132089866</v>
+        <v>132089853</v>
       </c>
       <c r="B7" t="n">
-        <v>96437</v>
+        <v>5199</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1217,34 +1217,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2667</v>
+        <v>105930</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Trestickan, Boh</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>316660</v>
+        <v>316907</v>
       </c>
       <c r="R7" t="n">
-        <v>6513174</v>
+        <v>6513455</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1287,6 +1292,21 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1303,10 +1323,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132089853</v>
+        <v>132089850</v>
       </c>
       <c r="B8" t="n">
-        <v>5199</v>
+        <v>8444</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1314,21 +1334,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>105930</v>
+        <v>106554</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1343,10 +1363,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>316907</v>
+        <v>316736</v>
       </c>
       <c r="R8" t="n">
-        <v>6513455</v>
+        <v>6513476</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1389,21 +1409,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1420,10 +1425,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132089850</v>
+        <v>132089866</v>
       </c>
       <c r="B9" t="n">
-        <v>8444</v>
+        <v>96438</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1431,39 +1436,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106554</v>
+        <v>2667</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Trestickan, Boh</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>316736</v>
+        <v>316660</v>
       </c>
       <c r="R9" t="n">
-        <v>6513476</v>
+        <v>6513174</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1522,10 +1522,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132089863</v>
+        <v>132089843</v>
       </c>
       <c r="B10" t="n">
-        <v>96439</v>
+        <v>91894</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1533,21 +1533,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2666</v>
+        <v>4660</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grov fjädermossa</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Exsertotheca crispa</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1557,10 +1557,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>316673</v>
+        <v>316707</v>
       </c>
       <c r="R10" t="n">
-        <v>6513287</v>
+        <v>6513460</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1603,6 +1603,21 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1619,10 +1634,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132089843</v>
+        <v>132089863</v>
       </c>
       <c r="B11" t="n">
-        <v>91893</v>
+        <v>96440</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1630,21 +1645,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4660</v>
+        <v>2666</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Grov fjädermossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Exsertotheca crispa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1654,10 +1669,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>316707</v>
+        <v>316673</v>
       </c>
       <c r="R11" t="n">
-        <v>6513460</v>
+        <v>6513287</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1700,21 +1715,6 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1734,7 +1734,7 @@
         <v>132089842</v>
       </c>
       <c r="B12" t="n">
-        <v>91893</v>
+        <v>91894</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2080,7 +2080,7 @@
         <v>132089855</v>
       </c>
       <c r="B15" t="n">
-        <v>57950</v>
+        <v>57951</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2200,7 +2200,7 @@
         <v>132089840</v>
       </c>
       <c r="B16" t="n">
-        <v>91872</v>
+        <v>91873</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2312,7 +2312,7 @@
         <v>132089851</v>
       </c>
       <c r="B17" t="n">
-        <v>96439</v>
+        <v>96440</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
         <v>132089848</v>
       </c>
       <c r="B18" t="n">
-        <v>96437</v>
+        <v>96438</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2521,7 +2521,7 @@
         <v>132089841</v>
       </c>
       <c r="B19" t="n">
-        <v>96439</v>
+        <v>96440</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2615,10 +2615,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132089865</v>
+        <v>132089845</v>
       </c>
       <c r="B20" t="n">
-        <v>96439</v>
+        <v>91967</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2626,21 +2626,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2666</v>
+        <v>5321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Grov fjädermossa</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Exsertotheca crispa</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2650,10 +2650,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>316663</v>
+        <v>316211</v>
       </c>
       <c r="R20" t="n">
-        <v>6513178</v>
+        <v>6513458</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2694,6 +2694,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2712,10 +2713,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132089845</v>
+        <v>132089865</v>
       </c>
       <c r="B21" t="n">
-        <v>91966</v>
+        <v>96440</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2723,21 +2724,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5321</v>
+        <v>2666</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Grov fjädermossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Exsertotheca crispa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2747,10 +2748,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>316211</v>
+        <v>316663</v>
       </c>
       <c r="R21" t="n">
-        <v>6513458</v>
+        <v>6513178</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2791,7 +2792,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2810,32 +2810,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132089862</v>
+        <v>132089861</v>
       </c>
       <c r="B22" t="n">
-        <v>92716</v>
+        <v>91967</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>717</v>
+        <v>5321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Borsttagging</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Gloiodon strigosus</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schwein. : Fr.) P. Karst.</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2845,10 +2845,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>316676</v>
+        <v>316813</v>
       </c>
       <c r="R22" t="n">
-        <v>6513293</v>
+        <v>6513496</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2889,6 +2889,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2922,32 +2923,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132089861</v>
+        <v>132089862</v>
       </c>
       <c r="B23" t="n">
-        <v>91966</v>
+        <v>92717</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5321</v>
+        <v>717</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Borsttagging</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Gloiodon strigosus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Schwein. : Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2957,10 +2958,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>316813</v>
+        <v>316676</v>
       </c>
       <c r="R23" t="n">
-        <v>6513496</v>
+        <v>6513293</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3001,7 +3002,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3038,7 +3038,7 @@
         <v>132089847</v>
       </c>
       <c r="B24" t="n">
-        <v>96439</v>
+        <v>96440</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 14156-2026 artfynd.xlsx
+++ b/artfynd/A 14156-2026 artfynd.xlsx
@@ -1323,10 +1323,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132089850</v>
+        <v>132089866</v>
       </c>
       <c r="B8" t="n">
-        <v>8444</v>
+        <v>96440</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1334,39 +1334,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106554</v>
+        <v>2667</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Trestickan, Boh</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>316736</v>
+        <v>316660</v>
       </c>
       <c r="R8" t="n">
-        <v>6513476</v>
+        <v>6513174</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1425,10 +1420,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132089866</v>
+        <v>132089850</v>
       </c>
       <c r="B9" t="n">
-        <v>96438</v>
+        <v>8444</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1436,34 +1431,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2667</v>
+        <v>106554</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Trestickan, Boh</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>316660</v>
+        <v>316736</v>
       </c>
       <c r="R9" t="n">
-        <v>6513174</v>
+        <v>6513476</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1525,7 +1525,7 @@
         <v>132089843</v>
       </c>
       <c r="B10" t="n">
-        <v>91894</v>
+        <v>91896</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>132089863</v>
       </c>
       <c r="B11" t="n">
-        <v>96440</v>
+        <v>96442</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1734,7 +1734,7 @@
         <v>132089842</v>
       </c>
       <c r="B12" t="n">
-        <v>91894</v>
+        <v>91896</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2200,7 +2200,7 @@
         <v>132089840</v>
       </c>
       <c r="B16" t="n">
-        <v>91873</v>
+        <v>91875</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2312,7 +2312,7 @@
         <v>132089851</v>
       </c>
       <c r="B17" t="n">
-        <v>96440</v>
+        <v>96442</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
         <v>132089848</v>
       </c>
       <c r="B18" t="n">
-        <v>96438</v>
+        <v>96440</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2521,7 +2521,7 @@
         <v>132089841</v>
       </c>
       <c r="B19" t="n">
-        <v>96440</v>
+        <v>96442</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2615,10 +2615,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132089845</v>
+        <v>132089865</v>
       </c>
       <c r="B20" t="n">
-        <v>91967</v>
+        <v>96442</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2626,21 +2626,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5321</v>
+        <v>2666</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Grov fjädermossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Exsertotheca crispa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2650,10 +2650,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>316211</v>
+        <v>316663</v>
       </c>
       <c r="R20" t="n">
-        <v>6513458</v>
+        <v>6513178</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2694,7 +2694,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2713,10 +2712,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132089865</v>
+        <v>132089845</v>
       </c>
       <c r="B21" t="n">
-        <v>96440</v>
+        <v>91969</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2724,21 +2723,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2666</v>
+        <v>5321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Grov fjädermossa</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Exsertotheca crispa</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2748,10 +2747,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>316663</v>
+        <v>316211</v>
       </c>
       <c r="R21" t="n">
-        <v>6513178</v>
+        <v>6513458</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2792,6 +2791,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2810,32 +2810,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132089861</v>
+        <v>132089862</v>
       </c>
       <c r="B22" t="n">
-        <v>91967</v>
+        <v>92719</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5321</v>
+        <v>717</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Borsttagging</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Gloiodon strigosus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Schwein. : Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2845,10 +2845,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>316813</v>
+        <v>316676</v>
       </c>
       <c r="R22" t="n">
-        <v>6513496</v>
+        <v>6513293</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2889,7 +2889,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2923,32 +2922,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132089862</v>
+        <v>132089861</v>
       </c>
       <c r="B23" t="n">
-        <v>92717</v>
+        <v>91969</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>717</v>
+        <v>5321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Borsttagging</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Gloiodon strigosus</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schwein. : Fr.) P. Karst.</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2958,10 +2957,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>316676</v>
+        <v>316813</v>
       </c>
       <c r="R23" t="n">
-        <v>6513293</v>
+        <v>6513496</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3002,6 +3001,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3038,7 +3038,7 @@
         <v>132089847</v>
       </c>
       <c r="B24" t="n">
-        <v>96440</v>
+        <v>96442</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 14156-2026 artfynd.xlsx
+++ b/artfynd/A 14156-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY28"/>
+  <dimension ref="A1:AY34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124571191</v>
+        <v>132089862</v>
       </c>
       <c r="B2" t="n">
-        <v>95345</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92790</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2810</v>
+        <v>717</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Borsttagging</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Gloiodon strigosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Schwein. : Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>316738</v>
+        <v>316676</v>
       </c>
       <c r="R2" t="n">
-        <v>6513434</v>
+        <v>6513293</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,17 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-04-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-04-27</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>mycket riklig</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -764,72 +754,81 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Tomas Fasth</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Tomas Fasth</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124571189</v>
+        <v>133163214</v>
       </c>
       <c r="B3" t="n">
-        <v>95436</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92790</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2666</v>
+        <v>717</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grov fjädermossa</t>
+          <t>Borsttagging</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Exsertotheca crispa</t>
+          <t>Gloiodon strigosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Schwein. : Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Trestickan, Boh</t>
+          <t>Trestickan, Trestickan, Boh</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>316738</v>
+        <v>316681</v>
       </c>
       <c r="R3" t="n">
-        <v>6513434</v>
+        <v>6513293</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -853,17 +852,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-04-27</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-04-27</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>riklig</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -878,12 +872,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Tomas Fasth</t>
+          <t>Christine Bryngelsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Tomas Fasth</t>
+          <t>Christine Bryngelsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -893,12 +887,7 @@
         <v>124571188</v>
       </c>
       <c r="B4" t="n">
-        <v>96781</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97785</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -992,15 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124571183</v>
+        <v>124571189</v>
       </c>
       <c r="B5" t="n">
-        <v>5176</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96439</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1008,33 +992,24 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100526</v>
+        <v>2666</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Grov fjädermossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Exsertotheca crispa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Trestickan, Boh</t>
@@ -1079,13 +1054,17 @@
           <t>2024-04-27</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>riklig</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1104,15 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124571185</v>
+        <v>132089841</v>
       </c>
       <c r="B6" t="n">
-        <v>80445</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96514</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1120,21 +1094,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>230185</v>
+        <v>2666</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Grov fjädermossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Exsertotheca crispa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1144,13 +1118,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>316738</v>
+        <v>316723</v>
       </c>
       <c r="R6" t="n">
-        <v>6513434</v>
+        <v>6513428</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1174,12 +1148,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-04-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-04-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1194,22 +1168,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Tomas Fasth</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Tomas Fasth</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132089853</v>
+        <v>132089847</v>
       </c>
       <c r="B7" t="n">
-        <v>5199</v>
+        <v>96514</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1217,39 +1191,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>105930</v>
+        <v>2666</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Grov fjädermossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Exsertotheca crispa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Trestickan, Boh</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>316907</v>
+        <v>316690</v>
       </c>
       <c r="R7" t="n">
-        <v>6513455</v>
+        <v>6513382</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1295,17 +1264,17 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1323,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132089866</v>
+        <v>132089851</v>
       </c>
       <c r="B8" t="n">
-        <v>96440</v>
+        <v>96514</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1334,16 +1303,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2667</v>
+        <v>2666</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Grov fjädermossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Exsertotheca crispa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1358,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>316660</v>
+        <v>316736</v>
       </c>
       <c r="R8" t="n">
-        <v>6513174</v>
+        <v>6513455</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1420,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132089850</v>
+        <v>132089863</v>
       </c>
       <c r="B9" t="n">
-        <v>8444</v>
+        <v>96514</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1431,39 +1400,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106554</v>
+        <v>2666</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Grov fjädermossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Exsertotheca crispa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Trestickan, Boh</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>316736</v>
+        <v>316673</v>
       </c>
       <c r="R9" t="n">
-        <v>6513476</v>
+        <v>6513287</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1522,10 +1486,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132089843</v>
+        <v>132089865</v>
       </c>
       <c r="B10" t="n">
-        <v>91896</v>
+        <v>96514</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1533,21 +1497,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4660</v>
+        <v>2666</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Grov fjädermossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Exsertotheca crispa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1557,10 +1521,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>316707</v>
+        <v>316663</v>
       </c>
       <c r="R10" t="n">
-        <v>6513460</v>
+        <v>6513178</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1603,21 +1567,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1634,10 +1583,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132089863</v>
+        <v>133161634</v>
       </c>
       <c r="B11" t="n">
-        <v>96442</v>
+        <v>96514</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1665,17 +1614,17 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Trestickan, Boh</t>
+          <t>Trestickan, Trestickan, Boh</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>316673</v>
+        <v>316724</v>
       </c>
       <c r="R11" t="n">
-        <v>6513287</v>
+        <v>6513400</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1699,12 +1648,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1719,22 +1668,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Christine Bryngelsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Christine Bryngelsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132089842</v>
+        <v>132089848</v>
       </c>
       <c r="B12" t="n">
-        <v>91896</v>
+        <v>96512</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1742,21 +1691,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4660</v>
+        <v>2667</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1766,10 +1715,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>316726</v>
+        <v>316690</v>
       </c>
       <c r="R12" t="n">
-        <v>6513488</v>
+        <v>6513382</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1843,10 +1792,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132089854</v>
+        <v>132089866</v>
       </c>
       <c r="B13" t="n">
-        <v>5179</v>
+        <v>96512</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1854,39 +1803,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100526</v>
+        <v>2667</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Trestickan, Boh</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>316907</v>
+        <v>316660</v>
       </c>
       <c r="R13" t="n">
-        <v>6513455</v>
+        <v>6513174</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1929,21 +1873,6 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -1960,10 +1889,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132089856</v>
+        <v>124571191</v>
       </c>
       <c r="B14" t="n">
-        <v>5199</v>
+        <v>96348</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1971,42 +1900,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>105930</v>
+        <v>2810</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Trestickan, Boh</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>316881</v>
+        <v>316738</v>
       </c>
       <c r="R14" t="n">
-        <v>6513474</v>
+        <v>6513434</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2030,12 +1954,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2024-04-27</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2024-04-27</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>mycket riklig</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2044,89 +1973,67 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Tomas Fasth</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Tomas Fasth</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132089855</v>
+        <v>133161261</v>
       </c>
       <c r="B15" t="n">
-        <v>57951</v>
+        <v>96423</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>2810</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Trestickan, Boh</t>
+          <t>Trestickan, Trestickan, Boh</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>316886</v>
+        <v>316657</v>
       </c>
       <c r="R15" t="n">
-        <v>6513452</v>
+        <v>6513377</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2150,12 +2057,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2166,41 +2073,26 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Christine Bryngelsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Christine Bryngelsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132089840</v>
+        <v>132089842</v>
       </c>
       <c r="B16" t="n">
-        <v>91875</v>
+        <v>91958</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2208,21 +2100,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5447</v>
+        <v>4660</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2232,10 +2124,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>316700</v>
+        <v>316726</v>
       </c>
       <c r="R16" t="n">
-        <v>6513265</v>
+        <v>6513488</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2281,17 +2173,17 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2309,10 +2201,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132089851</v>
+        <v>132089843</v>
       </c>
       <c r="B17" t="n">
-        <v>96442</v>
+        <v>91958</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2320,21 +2212,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2666</v>
+        <v>4660</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Grov fjädermossa</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Exsertotheca crispa</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2344,10 +2236,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>316736</v>
+        <v>316707</v>
       </c>
       <c r="R17" t="n">
-        <v>6513455</v>
+        <v>6513460</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2390,6 +2282,21 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2406,10 +2313,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132089848</v>
+        <v>132089844</v>
       </c>
       <c r="B18" t="n">
-        <v>96440</v>
+        <v>92031</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2417,21 +2324,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2667</v>
+        <v>5321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2441,10 +2348,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>316690</v>
+        <v>316380</v>
       </c>
       <c r="R18" t="n">
-        <v>6513382</v>
+        <v>6513603</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2485,23 +2392,9 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2518,10 +2411,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132089841</v>
+        <v>132089845</v>
       </c>
       <c r="B19" t="n">
-        <v>96442</v>
+        <v>92031</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2529,21 +2422,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2666</v>
+        <v>5321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Grov fjädermossa</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Exsertotheca crispa</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2553,10 +2446,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>316723</v>
+        <v>316211</v>
       </c>
       <c r="R19" t="n">
-        <v>6513428</v>
+        <v>6513458</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2597,6 +2490,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2615,10 +2509,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132089865</v>
+        <v>132089861</v>
       </c>
       <c r="B20" t="n">
-        <v>96442</v>
+        <v>92031</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2626,21 +2520,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2666</v>
+        <v>5321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Grov fjädermossa</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Exsertotheca crispa</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2650,10 +2544,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>316663</v>
+        <v>316813</v>
       </c>
       <c r="R20" t="n">
-        <v>6513178</v>
+        <v>6513496</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2694,8 +2588,24 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2712,10 +2622,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132089845</v>
+        <v>132089840</v>
       </c>
       <c r="B21" t="n">
-        <v>91969</v>
+        <v>91937</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2723,21 +2633,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5321</v>
+        <v>5447</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2747,10 +2657,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>316211</v>
+        <v>316700</v>
       </c>
       <c r="R21" t="n">
-        <v>6513458</v>
+        <v>6513265</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2791,9 +2701,23 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2810,32 +2734,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132089862</v>
+        <v>132089860</v>
       </c>
       <c r="B22" t="n">
-        <v>92719</v>
+        <v>75468</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>717</v>
+        <v>6426</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Borsttagging</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Gloiodon strigosus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schwein. : Fr.) P. Karst.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2845,10 +2769,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>316676</v>
+        <v>316828</v>
       </c>
       <c r="R22" t="n">
-        <v>6513293</v>
+        <v>6513500</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2891,21 +2815,6 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -2922,10 +2831,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132089861</v>
+        <v>132089855</v>
       </c>
       <c r="B23" t="n">
-        <v>91969</v>
+        <v>57972</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2933,34 +2842,42 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5321</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Trestickan, Boh</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>316813</v>
+        <v>316886</v>
       </c>
       <c r="R23" t="n">
-        <v>6513496</v>
+        <v>6513452</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3001,23 +2918,22 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3035,10 +2951,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132089847</v>
+        <v>124571202</v>
       </c>
       <c r="B24" t="n">
-        <v>96442</v>
+        <v>57141</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3046,37 +2962,42 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2666</v>
+        <v>100138</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Grov fjädermossa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Exsertotheca crispa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Trestickan, Boh</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>316690</v>
+        <v>316638</v>
       </c>
       <c r="R24" t="n">
-        <v>6513382</v>
+        <v>6513458</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3100,12 +3021,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2024-04-27</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2024-04-27</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3116,41 +3037,26 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Tomas Fasth</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Tomas Fasth</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133161634</v>
+        <v>124571203</v>
       </c>
       <c r="B25" t="n">
-        <v>96487</v>
+        <v>57141</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3158,34 +3064,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2666</v>
+        <v>100138</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Grov fjädermossa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Exsertotheca crispa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Trestickan, Trestickan, Boh</t>
+          <t>Trestickan, Boh</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>316724</v>
+        <v>316655</v>
       </c>
       <c r="R25" t="n">
-        <v>6513400</v>
+        <v>6513477</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3212,12 +3123,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2024-04-27</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2024-04-27</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3232,22 +3143,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Christine Bryngelsson</t>
+          <t>Tomas Fasth</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Christine Bryngelsson</t>
+          <t>Tomas Fasth</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133163347</v>
+        <v>132089852</v>
       </c>
       <c r="B26" t="n">
-        <v>8449</v>
+        <v>4776</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3255,37 +3166,42 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>106554</v>
+        <v>100299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Trestickan, Trestickan, Boh</t>
+          <t>Trestickan, Boh</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>316681</v>
+        <v>316928</v>
       </c>
       <c r="R26" t="n">
-        <v>6513293</v>
+        <v>6513492</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3309,12 +3225,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3325,64 +3241,88 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Christine Bryngelsson</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Christine Bryngelsson</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133163214</v>
+        <v>124571183</v>
       </c>
       <c r="B27" t="n">
-        <v>92763</v>
+        <v>5179</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>717</v>
+        <v>100526</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Borsttagging</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Gloiodon strigosus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schwein. : Fr.) P. Karst.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Trestickan, Trestickan, Boh</t>
+          <t>Trestickan, Boh</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>316681</v>
+        <v>316738</v>
       </c>
       <c r="R27" t="n">
-        <v>6513293</v>
+        <v>6513434</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3406,12 +3346,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2024-04-27</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2024-04-27</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3420,28 +3360,29 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Christine Bryngelsson</t>
+          <t>Tomas Fasth</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Christine Bryngelsson</t>
+          <t>Tomas Fasth</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133161261</v>
+        <v>132089854</v>
       </c>
       <c r="B28" t="n">
-        <v>96396</v>
+        <v>5181</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3449,37 +3390,42 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2810</v>
+        <v>100526</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Trestickan, Trestickan, Boh</t>
+          <t>Trestickan, Boh</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>316657</v>
+        <v>316907</v>
       </c>
       <c r="R28" t="n">
-        <v>6513377</v>
+        <v>6513455</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3503,12 +3449,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3519,19 +3465,681 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>132089853</v>
+      </c>
+      <c r="B29" t="n">
+        <v>5201</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Trestickan, Boh</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>316907</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6513455</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Munkedal</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Krokstad</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>132089856</v>
+      </c>
+      <c r="B30" t="n">
+        <v>5201</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Trestickan, Boh</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>316881</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6513474</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Munkedal</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Krokstad</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>132089859</v>
+      </c>
+      <c r="B31" t="n">
+        <v>5201</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Trestickan, Boh</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>316863</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6513490</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Munkedal</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Krokstad</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>132089850</v>
+      </c>
+      <c r="B32" t="n">
+        <v>8449</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Trestickan, Boh</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>316736</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6513476</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Munkedal</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Krokstad</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>133163347</v>
+      </c>
+      <c r="B33" t="n">
+        <v>8449</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Trestickan, Trestickan, Boh</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>316681</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6513293</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Munkedal</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Krokstad</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
           <t>Christine Bryngelsson</t>
         </is>
       </c>
-      <c r="AX28" t="inlineStr">
+      <c r="AX33" t="inlineStr">
         <is>
           <t>Christine Bryngelsson</t>
         </is>
       </c>
-      <c r="AY28" t="inlineStr"/>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>124571185</v>
+      </c>
+      <c r="B34" t="n">
+        <v>80992</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>230185</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Havstulpanlav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Thelotrema lepadinum</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Trestickan, Boh</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>316738</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6513434</v>
+      </c>
+      <c r="S34" t="n">
+        <v>50</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Munkedal</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Krokstad</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2024-04-27</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2024-04-27</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Tomas Fasth</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Tomas Fasth</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 14156-2026 artfynd.xlsx
+++ b/artfynd/A 14156-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY34"/>
+  <dimension ref="A1:AZ34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132089862</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -881,6 +891,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133163214</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124571188</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,6 +1100,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124571189</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132089841</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1289,6 +1319,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132089847</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1386,6 +1421,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132089851</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1483,6 +1523,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132089863</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1580,6 +1625,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132089865</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1677,6 +1727,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133161634</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1789,6 +1844,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132089848</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1886,6 +1946,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132089866</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1989,6 +2054,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124571191</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2086,6 +2156,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133161261</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2198,6 +2273,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132089842</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2310,6 +2390,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132089843</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2408,6 +2493,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132089844</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2506,6 +2596,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132089845</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2619,6 +2714,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132089861</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2731,6 +2831,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132089840</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2828,6 +2933,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132089860</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2948,6 +3058,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132089855</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3050,6 +3165,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124571202</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3152,6 +3272,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124571203</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3269,6 +3394,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132089852</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3376,6 +3506,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124571183</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3493,6 +3628,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132089854</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3610,6 +3750,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132089853</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3727,6 +3872,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132089856</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3844,6 +3994,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132089859</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3946,6 +4101,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132089850</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4043,6 +4203,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133163347</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4140,8 +4305,48 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124571185</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>